--- a/output/problem2_features.xlsx
+++ b/output/problem2_features.xlsx
@@ -697,7 +697,7 @@
         <v>0.631579</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>75.89</v>
+        <v>66.64</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -791,11 +791,11 @@
         <v>0.368421</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>47.61</v>
+        <v>71.2</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>及格</t>
+          <t>良好</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
         <v>0.263158</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>79.58</v>
+        <v>73.7</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>0.105263</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>64.31</v>
+        <v>62.44</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>0.736842</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>69.94</v>
+        <v>67.12</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>70.73</v>
+        <v>74.31</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>0.421053</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>74</v>
+        <v>65.39</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>0.368421</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>74.20999999999999</v>
+        <v>65.23</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>74.06</v>
+        <v>67.44</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>

--- a/output/problem2_features.xlsx
+++ b/output/problem2_features.xlsx
@@ -447,19 +447,19 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="32" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="32" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="21" max="21"/>
     <col width="18" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="16" customWidth="1" min="24" max="24"/>
@@ -487,12 +487,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>总页数</t>
+          <t>内容页数</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>总字符数</t>
+          <t>内容字符数</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>公式密度(公式数/总字符)</t>
+          <t>公式密度(公式数/内容字符)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>连词密度(连词数/总字符)</t>
+          <t>连词密度(连词数/内容字符)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -537,12 +537,12 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>总页数_归一</t>
+          <t>内容页数_归一</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>总字符数_归一</t>
+          <t>内容字符数_归一</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>公式密度(公式数/总字符)_归一</t>
+          <t>公式密度(公式数/内容字符)_归一</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>连词密度(连词数/总字符)_归一</t>
+          <t>连词密度(连词数/内容字符)_归一</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
@@ -628,76 +628,76 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>49297</v>
+        <v>19155</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.667</v>
+        <v>0.833</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>24.3</v>
+        <v>21.89</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>384</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.00779</v>
+        <v>0.005221</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.047</v>
+        <v>0.04</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>4</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>8.1e-05</v>
+        <v>0.000209</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N2" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.702913</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>0.479259</v>
+      </c>
+      <c r="Q2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="R2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="2" t="n">
-        <v>0.279371</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>0.992167</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>0.870651</v>
-      </c>
       <c r="S2" s="2" t="n">
-        <v>0.305195</v>
+        <v>0.4</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>0</v>
+        <v>0.07692300000000001</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0</v>
+        <v>0.028796</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.631579</v>
+        <v>0.529412</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.7365927499999999</v>
+        <v>0.6287929999999999</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>0.722671</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>0</v>
+        <v>0.0528595</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.631579</v>
+        <v>0.529412</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>66.64</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -722,76 +722,76 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>43441</v>
+        <v>14363</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.833</v>
+        <v>0.5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>20.9</v>
+        <v>20.76</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>387</v>
+        <v>62</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.008909</v>
+        <v>0.004317</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0.000209</v>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L3" s="2" t="n">
-        <v>9.2e-05</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="N3" s="2" t="n">
-        <v>0.686275</v>
+        <v>0.07692300000000001</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.843209</v>
+        <v>0.309643</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.593895</v>
+        <v>0.578994</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>1</v>
+        <v>0.608247</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>1</v>
+        <v>0.820207</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>0.051948</v>
+        <v>0</v>
       </c>
       <c r="T3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.009024000000000001</v>
+        <v>0.028796</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.368421</v>
+        <v>0.058824</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.73909475</v>
+        <v>0.36639</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.6839826666666666</v>
+        <v>0.4761513333333333</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>0.004512</v>
+        <v>0.014398</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.368421</v>
+        <v>0.058824</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>71.2</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -816,76 +816,76 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>21275</v>
+        <v>12141</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>23.23</v>
+        <v>21.23</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.006204</v>
+        <v>0.002965</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>15</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.000705</v>
+        <v>0.001235</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.235294</v>
+        <v>0.038462</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.249726</v>
+        <v>0.127288</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.378353</v>
+        <v>0.537511</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.334204</v>
+        <v>0.340206</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.687319</v>
+        <v>0.5513130000000001</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>0.149351</v>
+        <v>0</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0.916667</v>
+        <v>0.923077</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.511895</v>
+        <v>0.924084</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.263158</v>
+        <v>0.176471</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.38259325</v>
+        <v>0.30081525</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.3902913333333333</v>
+        <v>0.297173</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.7142809999999999</v>
+        <v>0.9235805</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.263158</v>
+        <v>0.176471</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>73.7</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -910,76 +910,76 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>11948</v>
+        <v>10590</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>16.97</v>
+        <v>16.78</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.006026</v>
+        <v>0.003211</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>14</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.001172</v>
+        <v>0.001322</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>5</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.078431</v>
+        <v>0.07692300000000001</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.957447</v>
+        <v>0.930274</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.177546</v>
+        <v>0.319588</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.666744</v>
+        <v>0.600239</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>0.181818</v>
+        <v>0</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.833333</v>
+        <v>0.846154</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.894996</v>
+        <v>1</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.105263</v>
+        <v>0.117647</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.4257195</v>
+        <v>0.37679925</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.342036</v>
+        <v>0.306609</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.8641645</v>
+        <v>0.9230769999999999</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.105263</v>
+        <v>0.117647</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>62.44</v>
+        <v>61.14</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1010,16 +1010,16 @@
         <v>15517</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>27.32</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.000258</v>
+        <v>0.000193</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0</v>
@@ -1034,10 +1034,10 @@
         <v>17</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.019608</v>
+        <v>0.038462</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.095558</v>
+        <v>0.40435</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>0</v>
@@ -1052,28 +1052,28 @@
         <v>0</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.25</v>
+        <v>0.307692</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.303527</v>
+        <v>0.239965</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.736842</v>
+        <v>0.823529</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.1955415</v>
+        <v>0.235703</v>
       </c>
       <c r="X6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.2767635</v>
+        <v>0.2738285</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.736842</v>
+        <v>0.823529</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>67.12</v>
+        <v>67.66</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1098,76 +1098,76 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>25352</v>
+        <v>22775</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.667</v>
+        <v>0.833</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>16.51</v>
+        <v>15.99</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.003037</v>
+        <v>0.002942</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.026</v>
+        <v>0.075</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>4</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.000158</v>
+        <v>0.000176</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.588235</v>
+        <v>1</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.358885</v>
+        <v>1</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.190601</v>
+        <v>0.659794</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.321235</v>
+        <v>0.5467379999999999</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>0.168831</v>
+        <v>0.75</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0</v>
+        <v>0.07692300000000001</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.063167</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.6535299999999999</v>
+        <v>0.95825</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.226889</v>
+        <v>0.6521773333333333</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.0315835</v>
+        <v>0.0384615</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>74.31</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1192,76 +1192,76 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>25438</v>
+        <v>14565</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>22.14</v>
+        <v>22.1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>170</v>
+        <v>37</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.006683</v>
+        <v>0.00254</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.076</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>9</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.000354</v>
+        <v>0.000618</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>11</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.313725</v>
+        <v>0.07692300000000001</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.361188</v>
+        <v>0.326221</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.479186</v>
+        <v>0.460724</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.43342</v>
+        <v>0.350515</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.742689</v>
+        <v>0.466786</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>0.493506</v>
+        <v>0</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0.416667</v>
+        <v>0.461538</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.223954</v>
+        <v>0.385689</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.421053</v>
+        <v>0.470588</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>0.45527475</v>
+        <v>0.382717</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.5565383333333334</v>
+        <v>0.2724336666666667</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.3203105</v>
+        <v>0.4236135</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.421053</v>
+        <v>0.470588</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>65.39</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1292,19 +1292,19 @@
         <v>12305</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.667</v>
+        <v>0.833</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>18.02</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.002113</v>
+        <v>0.002275</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.154</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>16</v>
@@ -1319,47 +1319,47 @@
         <v>0</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.009558000000000001</v>
+        <v>0.140747</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>0.8603150000000001</v>
+        <v>0.8208299999999999</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.057441</v>
+        <v>0.257732</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.214426</v>
+        <v>0.414081</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="T9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>1</v>
+        <v>0.980803</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.368421</v>
+        <v>0.411765</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.38421825</v>
+        <v>0.44864425</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.4239556666666667</v>
+        <v>0.4606043333333333</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>1</v>
+        <v>0.9904014999999999</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.368421</v>
+        <v>0.411765</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>65.23</v>
+        <v>64.89</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>良好</t>
+          <t>中等</t>
         </is>
       </c>
     </row>
@@ -1380,76 +1380,76 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>22869</v>
+        <v>18033</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0.833</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>22.8</v>
+        <v>22.94</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.004548</v>
+        <v>0.000555</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.067</v>
+        <v>0.1</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>10</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0.000437</v>
+        <v>0.000555</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.27451</v>
+        <v>0.269231</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.292404</v>
+        <v>0.610833</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>0.418131</v>
+        <v>0.386584</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>0.261097</v>
+        <v>0.07216500000000001</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.495896</v>
+        <v>0.07199700000000001</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>0.435065</v>
+        <v>1</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>0.5</v>
+        <v>0.538462</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.292043</v>
+        <v>0.330716</v>
       </c>
       <c r="V10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>0.45451125</v>
+        <v>0.5249119999999999</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>0.3973526666666667</v>
+        <v>0.3813873333333334</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0.3960215</v>
+        <v>0.434589</v>
       </c>
       <c r="Z10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>67.44</v>
+        <v>66.39</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>

--- a/output/problem2_features.xlsx
+++ b/output/problem2_features.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -452,21 +452,22 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="34" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="32" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="34" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="32" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
     <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
     <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,75 +538,80 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>内容页数_归一</t>
+          <t>内容页数_z</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>内容字符数_归一</t>
+          <t>内容字符数_z</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>段落平均长度_归一</t>
+          <t>章节完整度_z</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>公式总数_归一</t>
+          <t>段落平均长度_z</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>公式密度(公式数/内容字符)_归一</t>
+          <t>公式总数_z</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>规范编号公式占比_归一</t>
+          <t>公式密度(公式数/内容字符)_z</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>逻辑连词总频次_归一</t>
+          <t>规范编号公式占比_z</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>连词密度(连词数/内容字符)_归一</t>
+          <t>逻辑连词总频次_z</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>参考文献数量_归一</t>
+          <t>连词密度(连词数/内容字符)_z</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>参考文献数量_z</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>篇幅结构特征综合得分</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>公式特征综合得分</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>逻辑连接特征综合得分</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>参考文献特征综合得分</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>综合质量得分</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>等级</t>
         </is>
@@ -658,48 +664,51 @@
         <v>12</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.5</v>
+        <v>0.868986</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.702913</v>
+        <v>1.000723</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.479259</v>
+        <v>1.060306</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>1</v>
+        <v>-0.337465</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>1</v>
+        <v>2.046751</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>0.4</v>
+        <v>1.678333</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>0.07692300000000001</v>
+        <v>0.214879</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.028796</v>
+        <v>-1.081829</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.529412</v>
+        <v>-1.021235</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.6287929999999999</v>
+        <v>0.398726</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.6481375</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>0.0528595</v>
+        <v>1.313321</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.529412</v>
+        <v>-1.051532</v>
       </c>
       <c r="AA2" s="2" t="n">
+        <v>0.398726</v>
+      </c>
+      <c r="AB2" s="2" t="n">
         <v>65.18000000000001</v>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -752,48 +761,51 @@
         <v>4</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.07692300000000001</v>
+        <v>-0.496564</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.309643</v>
+        <v>-0.309076</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.578994</v>
+        <v>-1.061014</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>0.608247</v>
+        <v>0.006425</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.820207</v>
+        <v>0.70834</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>0</v>
+        <v>1.078644</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>0</v>
+        <v>-0.830477</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.028796</v>
+        <v>-1.293491</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.058824</v>
+        <v>-1.021235</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.36639</v>
+        <v>-1.036688</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.4761513333333333</v>
+        <v>-0.46505725</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>0.014398</v>
+        <v>0.3188356666666666</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.058824</v>
+        <v>-1.157363</v>
       </c>
       <c r="AA3" s="2" t="n">
+        <v>-1.036688</v>
+      </c>
+      <c r="AB3" s="2" t="n">
         <v>70.51000000000001</v>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
+      <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -846,48 +858,51 @@
         <v>6</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.038462</v>
+        <v>-0.620704</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.127288</v>
+        <v>-0.916416</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.537511</v>
+        <v>-1.061014</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.340206</v>
+        <v>-0.136609</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.5513130000000001</v>
+        <v>-0.207415</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>0</v>
+        <v>0.181764</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0.923077</v>
+        <v>-0.830477</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.924084</v>
+        <v>1.246455</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.176471</v>
+        <v>1.227235</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.30081525</v>
+        <v>-0.677834</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.297173</v>
+        <v>-0.68368575</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.9235805</v>
+        <v>-0.285376</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.176471</v>
+        <v>1.236845</v>
       </c>
       <c r="AA4" s="2" t="n">
+        <v>-0.677834</v>
+      </c>
+      <c r="AB4" s="2" t="n">
         <v>72.23999999999999</v>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
+      <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -940,48 +955,51 @@
         <v>5</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.07692300000000001</v>
+        <v>-0.496564</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
+        <v>-1.340351</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.930274</v>
+        <v>-1.061014</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.319588</v>
+        <v>1.217648</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.600239</v>
+        <v>-0.277857</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>0</v>
+        <v>0.344954</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.846154</v>
+        <v>-0.830477</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>1</v>
+        <v>1.034793</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.117647</v>
+        <v>1.417895</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.37679925</v>
+        <v>-0.8572610000000001</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.306609</v>
+        <v>-0.42007025</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.9230769999999999</v>
+        <v>-0.25446</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.117647</v>
+        <v>1.226344</v>
       </c>
       <c r="AA5" s="2" t="n">
+        <v>-0.8572610000000001</v>
+      </c>
+      <c r="AB5" s="2" t="n">
         <v>61.14</v>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
+      <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>中等</t>
         </is>
@@ -1034,48 +1052,51 @@
         <v>17</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.038462</v>
+        <v>-0.620704</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.40435</v>
+        <v>0.006347</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0</v>
+        <v>-1.061014</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0</v>
+        <v>-1.989963</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0</v>
+        <v>-1.369719</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>0</v>
+        <v>-1.657105</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.307692</v>
+        <v>-0.830477</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.239965</v>
+        <v>-0.446842</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.823529</v>
+        <v>-0.490894</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.235703</v>
+        <v>1.29586</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0</v>
+        <v>-0.9163334999999999</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.2738285</v>
+        <v>-1.285767</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.823529</v>
+        <v>-0.468868</v>
       </c>
       <c r="AA6" s="2" t="n">
+        <v>1.29586</v>
+      </c>
+      <c r="AB6" s="2" t="n">
         <v>67.66</v>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
+      <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -1128,48 +1149,51 @@
         <v>3</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1</v>
+        <v>2.482818</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1</v>
+        <v>1.990179</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>1</v>
+        <v>1.060306</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.659794</v>
+        <v>1.458067</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.5467379999999999</v>
+        <v>0.884447</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>0.75</v>
+        <v>0.166507</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.07692300000000001</v>
+        <v>1.129564</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0</v>
+        <v>-1.081829</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0</v>
+        <v>-1.093554</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.95825</v>
+        <v>-1.216115</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.6521773333333333</v>
+        <v>1.7478425</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.0384615</v>
+        <v>0.7268393333333334</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0</v>
+        <v>-1.0876915</v>
       </c>
       <c r="AA7" s="2" t="n">
+        <v>-1.216115</v>
+      </c>
+      <c r="AB7" s="2" t="n">
         <v>73.26000000000001</v>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
+      <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -1222,48 +1246,51 @@
         <v>11</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.07692300000000001</v>
+        <v>-0.496564</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.326221</v>
+        <v>-0.253863</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.460724</v>
+        <v>0.002831</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.350515</v>
+        <v>-0.401374</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.466786</v>
+        <v>-0.172193</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>0</v>
+        <v>-0.100169</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0.461538</v>
+        <v>-0.830477</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.385689</v>
+        <v>-0.023518</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.470588</v>
+        <v>-0.124915</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>0.382717</v>
+        <v>0.219299</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.2724336666666667</v>
+        <v>-0.2872425</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.4236135</v>
+        <v>-0.367613</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.470588</v>
+        <v>-0.0742165</v>
       </c>
       <c r="AA8" s="2" t="n">
+        <v>0.219299</v>
+      </c>
+      <c r="AB8" s="2" t="n">
         <v>65.18000000000001</v>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
+      <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -1316,48 +1343,51 @@
         <v>10</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0</v>
+        <v>-0.744845</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.140747</v>
+        <v>-0.87159</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>0.8208299999999999</v>
+        <v>1.060306</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.257732</v>
+        <v>0.840282</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.414081</v>
+        <v>-0.489185</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>0.71</v>
+        <v>-0.275963</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>1</v>
+        <v>1.025029</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.980803</v>
+        <v>1.458117</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.411765</v>
+        <v>1.369682</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.44864425</v>
+        <v>0.039873</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.4606043333333333</v>
+        <v>0.07103824999999997</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.9904014999999999</v>
+        <v>0.08662700000000001</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.411765</v>
+        <v>1.4138995</v>
       </c>
       <c r="AA9" s="2" t="n">
+        <v>0.039873</v>
+      </c>
+      <c r="AB9" s="2" t="n">
         <v>64.89</v>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
+      <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>中等</t>
         </is>
@@ -1410,48 +1440,51 @@
         <v>20</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.269231</v>
+        <v>0.124141</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.610833</v>
+        <v>0.6940460000000001</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>0.386584</v>
+        <v>1.060306</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>0.07216500000000001</v>
+        <v>-0.657009</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.07199700000000001</v>
+        <v>-1.123169</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>1</v>
+        <v>-1.416964</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>0.538462</v>
+        <v>1.782911</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.330716</v>
+        <v>0.188144</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>1</v>
+        <v>-0.262979</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>0.5249119999999999</v>
+        <v>1.83414</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>0.3813873333333334</v>
+        <v>0.305371</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0.434589</v>
+        <v>-0.2524073333333334</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>1</v>
+        <v>-0.03741750000000001</v>
       </c>
       <c r="AA10" s="2" t="n">
+        <v>1.83414</v>
+      </c>
+      <c r="AB10" s="2" t="n">
         <v>66.39</v>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
+      <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
